--- a/data/Greece_Ref._1689.xlsx
+++ b/data/Greece_Ref._1689.xlsx
@@ -10,12 +10,12 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="12" documentId="11_F25DC773A252ABDACC1048C8D99C6BDC5BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48D7EE1A-1B40-459F-B2A0-DD09C3627522}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="-460" yWindow="4140" windowWidth="14400" windowHeight="8180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" calcCompleted="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
